--- a/models/demo-hello-world/hello-world.xlsx
+++ b/models/demo-hello-world/hello-world.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shxie/Projects/anse-models/demo-hello-world/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7231F033-CD8C-BA4E-A599-E4826C338C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2570CC-4D1C-F745-BDAA-38E1ED52B66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="26980" activeTab="1" xr2:uid="{73351A0E-E394-C94F-8AB9-3EA9DA143F24}"/>
+    <workbookView xWindow="6840" yWindow="1160" windowWidth="25600" windowHeight="26900" xr2:uid="{73351A0E-E394-C94F-8AB9-3EA9DA143F24}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs - Flow Network" sheetId="1" r:id="rId1"/>
@@ -618,7 +618,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="128">
   <si>
     <t>COMMENT</t>
   </si>
@@ -1405,7 +1405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F935C300-5F44-C54A-ADD4-2A504DCCAD49}">
-  <dimension ref="A1:L112"/>
+  <dimension ref="B1:L112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.5703125" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
@@ -2168,7 +2168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="16" customHeight="1">
+    <row r="65" spans="2:8" ht="16" customHeight="1">
       <c r="B65" t="s">
         <v>54</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="16" customHeight="1">
+    <row r="66" spans="2:8" ht="16" customHeight="1">
       <c r="B66" t="s">
         <v>54</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="16" customHeight="1">
+    <row r="67" spans="2:8" ht="16" customHeight="1">
       <c r="B67" t="s">
         <v>54</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="16" customHeight="1">
+    <row r="69" spans="2:8" ht="16" customHeight="1">
       <c r="B69" t="s">
         <v>54</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="16" customHeight="1">
+    <row r="70" spans="2:8" ht="16" customHeight="1">
       <c r="B70" t="s">
         <v>54</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="16" customHeight="1">
+    <row r="71" spans="2:8" ht="16" customHeight="1">
       <c r="B71" t="s">
         <v>54</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="16" customHeight="1">
+    <row r="72" spans="2:8" ht="16" customHeight="1">
       <c r="B72" t="s">
         <v>54</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="16" customHeight="1">
+    <row r="73" spans="2:8" ht="16" customHeight="1">
       <c r="B73" t="s">
         <v>54</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="16" customHeight="1">
+    <row r="74" spans="2:8" ht="16" customHeight="1">
       <c r="B74" t="s">
         <v>54</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:8" s="3" customFormat="1" ht="16" customHeight="1">
+    <row r="76" spans="2:8" s="3" customFormat="1" ht="16" customHeight="1">
       <c r="B76" s="2" t="s">
         <v>55</v>
       </c>
@@ -2362,10 +2362,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="16" customHeight="1">
-      <c r="A78" t="s">
-        <v>0</v>
-      </c>
+    <row r="78" spans="2:8" ht="16" customHeight="1">
       <c r="B78" t="s">
         <v>60</v>
       </c>
@@ -2381,10 +2378,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="16" customHeight="1">
-      <c r="A79" t="s">
-        <v>0</v>
-      </c>
+    <row r="79" spans="2:8" ht="16" customHeight="1">
       <c r="B79" t="s">
         <v>60</v>
       </c>
@@ -2400,10 +2394,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="16" customHeight="1">
-      <c r="A80" t="s">
-        <v>0</v>
-      </c>
+    <row r="80" spans="2:8" ht="16" customHeight="1">
       <c r="B80" t="s">
         <v>60</v>
       </c>
@@ -2419,10 +2410,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="16" customHeight="1">
-      <c r="A81" t="s">
-        <v>0</v>
-      </c>
+    <row r="81" spans="2:10" ht="16" customHeight="1">
       <c r="B81" t="s">
         <v>60</v>
       </c>
@@ -2438,10 +2426,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="16" customHeight="1">
-      <c r="A82" t="s">
-        <v>0</v>
-      </c>
+    <row r="82" spans="2:10" ht="16" customHeight="1">
       <c r="B82" t="s">
         <v>60</v>
       </c>
@@ -2457,10 +2442,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="16" customHeight="1">
-      <c r="A83" t="s">
-        <v>0</v>
-      </c>
+    <row r="83" spans="2:10" ht="16" customHeight="1">
       <c r="B83" t="s">
         <v>60</v>
       </c>
@@ -2476,10 +2458,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="16" customHeight="1">
-      <c r="A84" t="s">
-        <v>0</v>
-      </c>
+    <row r="84" spans="2:10" ht="16" customHeight="1">
       <c r="B84" t="s">
         <v>60</v>
       </c>
@@ -2495,10 +2474,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="16" customHeight="1">
-      <c r="A85" t="s">
-        <v>0</v>
-      </c>
+    <row r="85" spans="2:10" ht="16" customHeight="1">
       <c r="B85" t="s">
         <v>60</v>
       </c>
@@ -2514,7 +2490,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:10" s="3" customFormat="1" ht="16" customHeight="1">
+    <row r="87" spans="2:10" s="3" customFormat="1" ht="16" customHeight="1">
       <c r="B87" s="2" t="s">
         <v>62</v>
       </c>
@@ -2543,7 +2519,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="16" customHeight="1">
+    <row r="89" spans="2:10" ht="16" customHeight="1">
       <c r="B89" t="s">
         <v>70</v>
       </c>
@@ -2558,7 +2534,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="16" customHeight="1">
+    <row r="90" spans="2:10" ht="16" customHeight="1">
       <c r="B90" t="s">
         <v>70</v>
       </c>
@@ -2573,7 +2549,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="16" customHeight="1">
+    <row r="92" spans="2:10" ht="16" customHeight="1">
       <c r="B92" t="s">
         <v>70</v>
       </c>
@@ -2588,7 +2564,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="16" customHeight="1">
+    <row r="93" spans="2:10" ht="16" customHeight="1">
       <c r="B93" t="s">
         <v>70</v>
       </c>
@@ -2603,7 +2579,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="16" customHeight="1">
+    <row r="95" spans="2:10" ht="16" customHeight="1">
       <c r="B95" t="s">
         <v>70</v>
       </c>
@@ -2618,7 +2594,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="16" customHeight="1">
+    <row r="96" spans="2:10" ht="16" customHeight="1">
       <c r="B96" t="s">
         <v>70</v>
       </c>

--- a/models/demo-hello-world/hello-world.xlsx
+++ b/models/demo-hello-world/hello-world.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shxie/Projects/anse-models/demo-hello-world/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shxie/projects/anse-models/demo-hello-world/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2570CC-4D1C-F745-BDAA-38E1ED52B66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80191983-F57D-5645-AA0A-3D89A4E44650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6840" yWindow="1160" windowWidth="25600" windowHeight="26900" xr2:uid="{73351A0E-E394-C94F-8AB9-3EA9DA143F24}"/>
+    <workbookView xWindow="6840" yWindow="600" windowWidth="25600" windowHeight="26880" xr2:uid="{73351A0E-E394-C94F-8AB9-3EA9DA143F24}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs - Flow Network" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Inputs - Spatial" sheetId="4" r:id="rId4"/>
     <sheet name="Inputs - Curves" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,6 +44,7 @@
   <authors>
     <author>Magnan, Michael</author>
     <author>mhafer</author>
+    <author>tc={FAB04036-A4D3-554A-816D-66D8F862EAE5}</author>
   </authors>
   <commentList>
     <comment ref="D1" authorId="0" shapeId="0" xr:uid="{DE5AEED7-5306-0F41-A9F6-E09723C07087}">
@@ -353,27 +354,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="G87" authorId="0" shapeId="0" xr:uid="{9D0C205B-9C9C-3F4A-912F-B707A4FF980A}">
+    <comment ref="G87" authorId="2" shapeId="0" xr:uid="{FAB04036-A4D3-554A-816D-66D8F862EAE5}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Magnan, Michael:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The physical state into which the C mass is transformed. Must supply a distinct Physical State here (not Physical State Group)
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>The physical state into which the C mass is transformed. Must supply a distinct Physical State here (not Physical State Group)</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -815,18 +802,9 @@
     <t>Proportion</t>
   </si>
   <si>
-    <t>Target Amount (Double precison)</t>
-  </si>
-  <si>
     <t>New Physical State Name</t>
   </si>
   <si>
-    <t>Filter By Physical State Name/Group</t>
-  </si>
-  <si>
-    <t>Filter By Species Name/Group</t>
-  </si>
-  <si>
     <t>Note</t>
   </si>
   <si>
@@ -1002,13 +980,22 @@
   </si>
   <si>
     <t>Usage</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Physical State Rule</t>
+  </si>
+  <si>
+    <t>Species Rule</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1038,8 +1025,14 @@
       <color theme="1"/>
       <name val="HelveticaNeue"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1050,6 +1043,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
@@ -1065,12 +1064,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1086,6 +1086,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Magnan, Michael" id="{7D4B715D-154F-2A43-AC0A-9588FB54B730}" userId="" providerId=""/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1403,6 +1409,15 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="G87" personId="{7D4B715D-154F-2A43-AC0A-9588FB54B730}" id="{FAB04036-A4D3-554A-816D-66D8F862EAE5}">
+    <text xml:space="preserve">The physical state into which the C mass is transformed. Must supply a distinct Physical State here (not Physical State Group)
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F935C300-5F44-C54A-ADD4-2A504DCCAD49}">
   <dimension ref="B1:L112"/>
@@ -1532,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="16" customHeight="1">
@@ -1568,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="16" customHeight="1">
@@ -1604,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="16" customHeight="1">
@@ -2503,25 +2518,25 @@
       <c r="E87" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F87" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G87" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G87" s="3" t="s">
+      <c r="H87" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="J87" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="J87" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="89" spans="2:10" ht="16" customHeight="1">
       <c r="B89" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C89" t="str" cm="1">
         <f t="array" ref="C89">C78</f>
@@ -2536,7 +2551,7 @@
     </row>
     <row r="90" spans="2:10" ht="16" customHeight="1">
       <c r="B90" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C90" t="str" cm="1">
         <f t="array" ref="C90">C78</f>
@@ -2551,7 +2566,7 @@
     </row>
     <row r="92" spans="2:10" ht="16" customHeight="1">
       <c r="B92" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C92" t="str" cm="1">
         <f t="array" ref="C92">C79</f>
@@ -2566,7 +2581,7 @@
     </row>
     <row r="93" spans="2:10" ht="16" customHeight="1">
       <c r="B93" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C93" t="str" cm="1">
         <f t="array" ref="C93">C79</f>
@@ -2581,7 +2596,7 @@
     </row>
     <row r="95" spans="2:10" ht="16" customHeight="1">
       <c r="B95" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C95" t="str" cm="1">
         <f t="array" ref="C95">C80</f>
@@ -2596,7 +2611,7 @@
     </row>
     <row r="96" spans="2:10" ht="16" customHeight="1">
       <c r="B96" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C96" t="str" cm="1">
         <f t="array" ref="C96">C80</f>
@@ -2611,7 +2626,7 @@
     </row>
     <row r="98" spans="2:5" ht="16" customHeight="1">
       <c r="B98" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C98" t="str" cm="1">
         <f t="array" ref="C98">C81</f>
@@ -2626,7 +2641,7 @@
     </row>
     <row r="99" spans="2:5" ht="16" customHeight="1">
       <c r="B99" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C99" t="str" cm="1">
         <f t="array" ref="C99">C81</f>
@@ -2641,7 +2656,7 @@
     </row>
     <row r="101" spans="2:5" ht="16" customHeight="1">
       <c r="B101" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C101" t="str" cm="1">
         <f t="array" ref="C101">C82</f>
@@ -2656,7 +2671,7 @@
     </row>
     <row r="102" spans="2:5" ht="16" customHeight="1">
       <c r="B102" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C102" t="str" cm="1">
         <f t="array" ref="C102">C82</f>
@@ -2671,7 +2686,7 @@
     </row>
     <row r="104" spans="2:5" ht="16" customHeight="1">
       <c r="B104" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C104" t="str" cm="1">
         <f t="array" ref="C104">C83</f>
@@ -2686,7 +2701,7 @@
     </row>
     <row r="105" spans="2:5" ht="16" customHeight="1">
       <c r="B105" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C105" t="str" cm="1">
         <f t="array" ref="C105">C83</f>
@@ -2701,7 +2716,7 @@
     </row>
     <row r="107" spans="2:5" ht="16" customHeight="1">
       <c r="B107" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C107" t="str" cm="1">
         <f t="array" ref="C107">C84</f>
@@ -2716,7 +2731,7 @@
     </row>
     <row r="108" spans="2:5" ht="16" customHeight="1">
       <c r="B108" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C108" t="str" cm="1">
         <f t="array" ref="C108">C84</f>
@@ -2731,7 +2746,7 @@
     </row>
     <row r="110" spans="2:5" ht="16" customHeight="1">
       <c r="B110" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C110" t="str" cm="1">
         <f t="array" ref="C110">C85</f>
@@ -2746,7 +2761,7 @@
     </row>
     <row r="111" spans="2:5" ht="16" customHeight="1">
       <c r="B111" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C111" t="str" cm="1">
         <f t="array" ref="C111">C85</f>
@@ -2761,7 +2776,7 @@
     </row>
     <row r="112" spans="2:5" ht="16" customHeight="1">
       <c r="B112" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C112" t="str" cm="1">
         <f t="array" ref="C112">C85</f>
@@ -2797,31 +2812,31 @@
   <sheetData>
     <row r="1" spans="2:11" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="I1" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>59</v>
@@ -2829,7 +2844,7 @@
     </row>
     <row r="3" spans="2:11">
       <c r="B3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C3" t="str">
         <f>'Inputs - Flow Network'!C3</f>
@@ -2871,26 +2886,26 @@
   <sheetData>
     <row r="1" spans="2:7" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="2:7">
       <c r="B3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="2:7" s="3" customFormat="1">
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>2</v>
@@ -2904,27 +2919,27 @@
     </row>
     <row r="7" spans="2:7" s="3" customFormat="1">
       <c r="B7" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="2:7" s="3" customFormat="1">
       <c r="B9" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>58</v>
@@ -2935,7 +2950,7 @@
     </row>
     <row r="11" spans="2:7" s="3" customFormat="1">
       <c r="B11" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>2</v>
@@ -2949,24 +2964,24 @@
     </row>
     <row r="13" spans="2:7" s="3" customFormat="1">
       <c r="B13" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="2:7" s="3" customFormat="1">
       <c r="B15" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>59</v>
@@ -2995,22 +3010,22 @@
   <sheetData>
     <row r="1" spans="1:8" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>59</v>
@@ -3021,13 +3036,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3038,13 +3053,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3052,7 +3067,7 @@
     </row>
     <row r="5" spans="1:8" s="3" customFormat="1">
       <c r="B5" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>2</v>
@@ -3063,21 +3078,21 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="3" customFormat="1">
       <c r="B8" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>59</v>
@@ -3088,27 +3103,27 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="3" customFormat="1">
       <c r="B12" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3116,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -3130,10 +3145,10 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -3159,13 +3174,13 @@
   <sheetData>
     <row r="1" spans="2:6" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>58</v>
@@ -3176,7 +3191,7 @@
     </row>
     <row r="3" spans="2:6" s="3" customFormat="1">
       <c r="B3" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>2</v>
@@ -3190,33 +3205,33 @@
     </row>
     <row r="5" spans="2:6" s="3" customFormat="1">
       <c r="B5" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>36</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="2:6" s="3" customFormat="1">
       <c r="B7" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
